--- a/BIS05D.xlsx
+++ b/BIS05D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="475">
   <si>
     <t/>
   </si>
@@ -442,12 +442,6 @@
     <t>NABATI WRPZ STRW 66G</t>
   </si>
   <si>
-    <t>20137573</t>
-  </si>
-  <si>
-    <t>NABATI BIG RL CHO56G</t>
-  </si>
-  <si>
     <t>20137570</t>
   </si>
   <si>
@@ -637,10 +631,10 @@
     <t>MONDE BISC PBIS 190G</t>
   </si>
   <si>
-    <t>20135800</t>
-  </si>
-  <si>
-    <t>JULIES LEMOND CHS 89</t>
+    <t>20085046</t>
+  </si>
+  <si>
+    <t>JULIES PNUT BTR 82.5</t>
   </si>
   <si>
     <t>18</t>
@@ -649,12 +643,6 @@
     <t>RT,(E-3.5B)</t>
   </si>
   <si>
-    <t>20085046</t>
-  </si>
-  <si>
-    <t>JULIES PNUT BTR 82.5</t>
-  </si>
-  <si>
     <t>20057475</t>
   </si>
   <si>
@@ -916,12 +904,6 @@
     <t>28</t>
   </si>
   <si>
-    <t>20095146</t>
-  </si>
-  <si>
-    <t>MONDE SRN EGG ORI 70</t>
-  </si>
-  <si>
     <t>10036931</t>
   </si>
   <si>
@@ -1036,12 +1018,6 @@
     <t>ROMA ARDEN CHOCO 72G</t>
   </si>
   <si>
-    <t>20133641</t>
-  </si>
-  <si>
-    <t>ROMA ARDEN STRWBRY72</t>
-  </si>
-  <si>
     <t>20033519</t>
   </si>
   <si>
@@ -1301,12 +1277,6 @@
   </si>
   <si>
     <t>NSIN BSC KLP IJO 280</t>
-  </si>
-  <si>
-    <t>20138040</t>
-  </si>
-  <si>
-    <t>ROMA LAVITA MILK 210</t>
   </si>
   <si>
     <t>20133020</t>
@@ -1858,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3142,7 +3112,7 @@
         <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -3162,7 +3132,7 @@
         <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3182,7 +3152,7 @@
         <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3202,7 +3172,7 @@
         <v>140</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -3222,7 +3192,7 @@
         <v>140</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>5</v>
@@ -3242,10 +3212,10 @@
         <v>140</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3259,27 +3229,27 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -3299,10 +3269,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3319,13 +3289,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3339,10 +3309,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>24</v>
@@ -3359,13 +3329,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3379,10 +3349,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3399,10 +3369,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3419,10 +3389,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3430,19 +3400,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3459,10 +3429,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3479,10 +3449,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3499,10 +3469,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3519,10 +3489,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3539,10 +3509,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3559,10 +3529,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3579,10 +3549,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3599,10 +3569,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3619,10 +3589,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3630,19 +3600,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3659,10 +3629,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3679,10 +3649,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3699,10 +3669,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3719,10 +3689,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3739,33 +3709,33 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>211</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3779,13 +3749,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3799,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3810,39 +3780,39 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3859,10 +3829,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3879,10 +3849,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3890,19 +3860,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3910,19 +3880,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3939,10 +3909,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3959,10 +3929,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3970,19 +3940,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3990,19 +3960,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -4019,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -4039,10 +4009,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -4050,19 +4020,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4070,16 +4040,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>4</v>
@@ -4090,16 +4060,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>8</v>
@@ -4110,16 +4080,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>4</v>
@@ -4130,16 +4100,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -4150,19 +4120,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4179,90 +4149,90 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4279,10 +4249,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4299,13 +4269,13 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,13 +4289,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,10 +4309,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>24</v>
@@ -4359,13 +4329,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4379,30 +4349,30 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>24</v>
+        <v>282</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4410,39 +4380,39 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>286</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4459,13 +4429,13 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,13 +4449,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4499,50 +4469,50 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4559,10 +4529,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4579,10 +4549,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4590,19 +4560,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4610,19 +4580,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4630,16 +4600,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>4</v>
@@ -4650,16 +4620,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
@@ -4670,16 +4640,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>11</v>
@@ -4690,22 +4660,22 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,10 +4689,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4730,19 +4700,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4750,39 +4720,39 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4799,10 +4769,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4819,10 +4789,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4830,19 +4800,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4850,19 +4820,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4870,19 +4840,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4890,19 +4860,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4910,19 +4880,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4930,16 +4900,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>4</v>
@@ -4950,16 +4920,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>8</v>
@@ -4970,16 +4940,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>11</v>
@@ -4990,16 +4960,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>14</v>
@@ -5010,16 +4980,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
@@ -5030,16 +5000,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>354</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -5050,16 +5020,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>11</v>
@@ -5070,16 +5040,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>14</v>
@@ -5090,16 +5060,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>4</v>
@@ -5110,16 +5080,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>8</v>
@@ -5130,59 +5100,59 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5199,10 +5169,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5219,13 +5189,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5239,13 +5209,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5259,10 +5229,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5279,50 +5249,50 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>383</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5330,62 +5300,62 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>18</v>
+        <v>383</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5399,30 +5369,30 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>18</v>
@@ -5430,136 +5400,136 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -5570,16 +5540,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
@@ -5590,36 +5560,36 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
@@ -5630,16 +5600,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>4</v>
@@ -5650,16 +5620,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>8</v>
@@ -5670,36 +5640,36 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>18</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>14</v>
@@ -5710,16 +5680,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>17</v>
@@ -5730,16 +5700,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>4</v>
@@ -5750,16 +5720,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B195" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>434</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>8</v>
@@ -5770,39 +5740,39 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>439</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5810,19 +5780,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5830,19 +5800,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5859,10 +5829,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5879,10 +5849,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5890,19 +5860,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E202" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5910,19 +5880,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5930,19 +5900,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5950,19 +5920,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5970,19 +5940,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5999,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -6010,19 +5980,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>461</v>
-      </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -6030,19 +6000,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -6050,19 +6020,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6070,19 +6040,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6090,121 +6060,21 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A213" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A214" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F214" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A215" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E215" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F216" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A217" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F217" s="1" t="s">
         <v>5</v>
       </c>
     </row>
